--- a/nodes_source_analyses/energy/transport/transport_bus_using_electricity.converter.xlsx
+++ b/nodes_source_analyses/energy/transport/transport_bus_using_electricity.converter.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10621"/>
   <workbookPr showInkAnnotation="0" codeName="ThisWorkbook" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mathijsbijkerk/Projects/etdataset/nodes_source_analyses/energy/transport/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/robin/Desktop/Quintel/etdataset/nodes_source_analyses/energy/transport/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6490C9A2-8303-0C48-90B1-1B26C05793FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6541E914-774E-0B44-A732-6E6500BA3EA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60160" yWindow="-18040" windowWidth="30080" windowHeight="16080" tabRatio="762" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38940" yWindow="660" windowWidth="36140" windowHeight="21100" tabRatio="762" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover sheet" sheetId="14" r:id="rId1"/>
@@ -37,7 +37,7 @@
     <definedName name="Wp_to_kWp">#REF!</definedName>
     <definedName name="WP_to_MWp">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029" concurrentManualCount="4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr defaultImageDpi="32767"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="121">
   <si>
     <t>Source</t>
   </si>
@@ -126,9 +126,6 @@
     <t>free_co2_factor</t>
   </si>
   <si>
-    <t>http://www.fuelswitch.nl/files/files_news/natural_gas_in_transport_tno_ce_delft_ecn_4818.pdf</t>
-  </si>
-  <si>
     <t>Author</t>
   </si>
   <si>
@@ -198,16 +195,10 @@
     <t>ETM Library URL</t>
   </si>
   <si>
-    <t>http://refman.et-model.com/publications/1928</t>
-  </si>
-  <si>
     <t>MJ/km</t>
   </si>
   <si>
     <t>km/MJ</t>
-  </si>
-  <si>
-    <t>p.66</t>
   </si>
   <si>
     <t>Efficiency</t>
@@ -217,79 +208,13 @@
 </t>
   </si>
   <si>
-    <t>Eurostat</t>
-  </si>
-  <si>
-    <t>2017</t>
-  </si>
-  <si>
-    <t>vehicle km</t>
-  </si>
-  <si>
-    <t>mln vehicle km</t>
-  </si>
-  <si>
-    <t>CBS</t>
-  </si>
-  <si>
-    <t>http://statline.cbs.nl/Statweb/publication/?DM=SLNL&amp;PA=83497ned&amp;D1=0&amp;D2=a&amp;D3=0&amp;D4=5&amp;HDR=T,G3&amp;STB=G1,G2&amp;VW=T</t>
-  </si>
-  <si>
-    <t>Passenger kilometers bus/tram/metro</t>
-  </si>
-  <si>
-    <t>Passenger kilometers tram/metro</t>
-  </si>
-  <si>
-    <t>https://ec.europa.eu/transport/sites/transport/files/pb2017-section22.xls</t>
-  </si>
-  <si>
-    <t>passenger km</t>
-  </si>
-  <si>
     <t>passenger km/vehicle km</t>
   </si>
   <si>
     <t>passenger km/MJ</t>
   </si>
   <si>
-    <t>mld passenger km</t>
-  </si>
-  <si>
-    <t>Reizigerskilometers:</t>
-  </si>
-  <si>
-    <t>5.8 mld voor bus/tram/metro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">min 0.9 mld voor bus/tram. </t>
-  </si>
-  <si>
-    <t>http://statline.cbs.nl/Statweb/publication/?DM=SLNL&amp;PA=80589NED&amp;D1=0&amp;D2=a&amp;D3=0&amp;D4=25&amp;HDR=T&amp;STB=G2,G3,G1&amp;VW=T</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Touringcars zitten hier nog niet bij, die vallen onder de categorie overige vervoerwijze bij CBS. </t>
-  </si>
-  <si>
-    <t>Schatting: dit gaat om 3.96 mld reizigerskilometers</t>
-  </si>
-  <si>
-    <t>Aanname is gebaseerd op: Totaal aantal touringcarkilometers is ongeveer 23% van het totaal aantal buskilometers (CBS). De bezettingsgraad van touring cars is ongeveer 3.5 keer hoger dan van lijnbussen (CE Delft). Dus we tellen 80% van de lijnbusreizigerskilometers op bij het totaal (+3.96)</t>
-  </si>
-  <si>
     <t>CE Delft</t>
-  </si>
-  <si>
-    <t>Vehicle kilometers bus (touringcar en lijnbus)</t>
-  </si>
-  <si>
-    <t>Occupancy rates touringcar / public transport bus</t>
-  </si>
-  <si>
-    <t>https://refman.energytransitionmodel.com/publications/2072</t>
-  </si>
-  <si>
-    <t>http://www.ce.nl/publicatie/stream_personenvervoer_2014/1478</t>
   </si>
   <si>
     <t>output.passenger_kms</t>
@@ -485,9 +410,6 @@
     <t>transport_bus_using_electricity.converter.ad</t>
   </si>
   <si>
-    <t>Marlieke Verweij</t>
-  </si>
-  <si>
     <t>Quintel assumption</t>
   </si>
   <si>
@@ -507,6 +429,24 @@
   </si>
   <si>
     <t>storage decay per month</t>
+  </si>
+  <si>
+    <t> https://ce.nl/wp-content/uploads/2025/02/CE_Delft_210506_STREAM_Personenvervoer_2024_Def.pdf</t>
+  </si>
+  <si>
+    <t>p. 39</t>
+  </si>
+  <si>
+    <t>p. 18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CE Delft </t>
+  </si>
+  <si>
+    <t>Robin de Smit</t>
+  </si>
+  <si>
+    <t>CE Delft (2024)</t>
   </si>
 </sst>
 </file>
@@ -528,6 +468,13 @@
       <color theme="1"/>
       <name val="Lettertype hoofdtekst"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -734,13 +681,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1055,454 +995,446 @@
   </borders>
   <cellStyleXfs count="244">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="32" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="155">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="23" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="24" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="19" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="18" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="13" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="13" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="23" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="12" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="12" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="22" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="22" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="27" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="27" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="28" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="28" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="5" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="28" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="27" fillId="2" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="33" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="169" fontId="33" fillId="0" borderId="18" xfId="243" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="33" fillId="2" borderId="18" xfId="243" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="170" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="2" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="22" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="23" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="9" fontId="12" fillId="2" borderId="0" xfId="243" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="9" fontId="11" fillId="2" borderId="0" xfId="243" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="244">
     <cellStyle name="Followed Hyperlink" xfId="2" builtinId="9" hidden="1"/>
@@ -1767,403 +1699,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>177800</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>139700</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="Picture 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000009000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6527800" y="546100"/>
-          <a:ext cx="7264400" cy="2590800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>88900</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>292100</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>95533</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="10" name="Group 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00000A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="8775700" y="3149600"/>
-          <a:ext cx="6781800" cy="2279933"/>
-          <a:chOff x="9231573" y="32137067"/>
-          <a:chExt cx="12902777" cy="4417646"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="11" name="Picture 10">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00000B000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="9231573" y="32137067"/>
-            <a:ext cx="12902777" cy="4417646"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="12" name="Rectangle 11">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00000C000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="13162773" y="34809804"/>
-            <a:ext cx="1173709" cy="378631"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
-            <a:solidFill>
-              <a:srgbClr val="FFC000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="3">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="2">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr lang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>584200</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>88899</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
-    </xdr:to>
-    <xdr:grpSp>
-      <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="13" name="Group 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00000D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGrpSpPr/>
-      </xdr:nvGrpSpPr>
-      <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="9245600" y="6832600"/>
-          <a:ext cx="13830299" cy="2514600"/>
-          <a:chOff x="9702800" y="37896800"/>
-          <a:chExt cx="16776701" cy="4152900"/>
-        </a:xfrm>
-      </xdr:grpSpPr>
-      <xdr:pic>
-        <xdr:nvPicPr>
-          <xdr:cNvPr id="14" name="Picture 13">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00000E000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvPicPr>
-            <a:picLocks noChangeAspect="1"/>
-          </xdr:cNvPicPr>
-        </xdr:nvPicPr>
-        <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-          <a:stretch>
-            <a:fillRect/>
-          </a:stretch>
-        </xdr:blipFill>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="9702800" y="37896800"/>
-            <a:ext cx="16776701" cy="4152900"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-        </xdr:spPr>
-      </xdr:pic>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="15" name="Rectangle 14">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-00000F000000}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="13250987" y="41388162"/>
-            <a:ext cx="1654792" cy="368489"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:noFill/>
-          <a:ln>
-            <a:solidFill>
-              <a:srgbClr val="FFC000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="3">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="2">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr lang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
-    </xdr:grpSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2336800" cy="1600200"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="Picture 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000010000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5791200" y="9486900"/>
-          <a:ext cx="2336800" cy="1600200"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>469900</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>723900</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>186986</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8407400" y="9537700"/>
-          <a:ext cx="6794500" cy="1888786"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>241300</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>25400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>78</xdr:row>
-      <xdr:rowOff>82513</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0400-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5765800" y="11671300"/>
-          <a:ext cx="7327900" cy="4324313"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>3</xdr:col>
       <xdr:colOff>431800</xdr:colOff>
       <xdr:row>80</xdr:row>
@@ -2189,7 +1724,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2233,7 +1768,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2252,23 +1787,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>1536700</xdr:colOff>
-      <xdr:row>125</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>640427</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>206238</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>698500</xdr:colOff>
-      <xdr:row>146</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>293511</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>35788</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6">
+        <xdr:cNvPr id="18" name="Picture 17">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{52C34CA9-FD15-9A4A-9B0B-1065E4BE2D88}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F8C5827-1046-5CE8-CA82-E2DD5061A5C0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2277,15 +1812,15 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8978900" y="25692100"/>
-          <a:ext cx="2336800" cy="4330700"/>
+          <a:off x="7272649" y="1454529"/>
+          <a:ext cx="7772400" cy="1479464"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2294,12 +1829,187 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>607863</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>173675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>423333</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>89645</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="Rectangle 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3F83AA3-3A4D-9A47-8DDD-748A0848F327}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7240085" y="2246923"/>
+          <a:ext cx="3810000" cy="328448"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>466752</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>173676</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>33701</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>59376</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="Picture 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4EF88F46-CEC4-2847-8BFB-41B200900BB8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7098974" y="2865642"/>
+          <a:ext cx="14285924" cy="8135272"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>54272</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>195385</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>309900</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>195385</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="Rectangle 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFF087CA-7D06-7F45-961A-989D07962EBD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9096238" y="10311966"/>
+          <a:ext cx="4315286" cy="412479"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-GB" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:relativeUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Cover Sheet"/>
       <sheetName val="Changelog"/>
@@ -2736,12 +2446,12 @@
     <tabColor theme="0"/>
   </sheetPr>
   <dimension ref="A1:C23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="3.140625" style="19" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="12" customWidth="1"/>
-    <col min="3" max="3" width="38.42578125" style="12" customWidth="1"/>
-    <col min="4" max="16384" width="10.85546875" style="12"/>
+    <col min="1" max="1" width="3.1640625" style="19" customWidth="1"/>
+    <col min="2" max="2" width="11.5" style="12" customWidth="1"/>
+    <col min="3" max="3" width="38.5" style="12" customWidth="1"/>
+    <col min="4" max="16384" width="10.83203125" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="17" customFormat="1">
@@ -2767,16 +2477,16 @@
         <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>132</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1"/>
       <c r="B5" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2801,7 +2511,7 @@
     <row r="9" spans="1:3">
       <c r="A9" s="1"/>
       <c r="B9" s="36" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C9" s="37"/>
     </row>
@@ -2813,31 +2523,31 @@
     <row r="11" spans="1:3">
       <c r="A11" s="1"/>
       <c r="B11" s="38" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" s="40" t="s">
         <v>24</v>
-      </c>
-      <c r="C11" s="40" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="17" thickBot="1">
       <c r="A12" s="1"/>
       <c r="B12" s="38"/>
       <c r="C12" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="17" thickBot="1">
       <c r="A13" s="1"/>
       <c r="B13" s="38"/>
       <c r="C13" s="41" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="1"/>
       <c r="B14" s="38"/>
       <c r="C14" s="39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2848,58 +2558,58 @@
     <row r="16" spans="1:3">
       <c r="A16" s="1"/>
       <c r="B16" s="38" t="s">
+        <v>28</v>
+      </c>
+      <c r="C16" s="42" t="s">
         <v>29</v>
-      </c>
-      <c r="C16" s="42" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="1"/>
       <c r="B17" s="38"/>
       <c r="C17" s="43" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="1"/>
       <c r="B18" s="38"/>
       <c r="C18" s="44" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="1"/>
       <c r="B19" s="38"/>
       <c r="C19" s="45" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="1"/>
       <c r="B20" s="46"/>
       <c r="C20" s="47" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="1"/>
       <c r="B21" s="46"/>
       <c r="C21" s="48" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" s="1"/>
       <c r="B22" s="46"/>
       <c r="C22" s="49" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="B23" s="46"/>
       <c r="C23" s="50" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -2914,54 +2624,54 @@
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
   <dimension ref="B2:J38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="3.140625" style="23" customWidth="1"/>
-    <col min="2" max="2" width="3.42578125" style="23" customWidth="1"/>
-    <col min="3" max="3" width="33.85546875" style="23" customWidth="1"/>
-    <col min="4" max="4" width="12.42578125" style="23" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" style="23" customWidth="1"/>
-    <col min="6" max="6" width="4.42578125" style="23" customWidth="1"/>
-    <col min="7" max="7" width="44.140625" style="23" customWidth="1"/>
-    <col min="8" max="8" width="2.42578125" style="23" customWidth="1"/>
-    <col min="9" max="9" width="42.42578125" style="23" customWidth="1"/>
-    <col min="10" max="10" width="3.42578125" style="23" customWidth="1"/>
-    <col min="11" max="16384" width="10.85546875" style="23"/>
+    <col min="1" max="1" width="3.1640625" style="23" customWidth="1"/>
+    <col min="2" max="2" width="3.5" style="23" customWidth="1"/>
+    <col min="3" max="3" width="33.83203125" style="23" customWidth="1"/>
+    <col min="4" max="4" width="12.5" style="23" customWidth="1"/>
+    <col min="5" max="5" width="17.5" style="23" customWidth="1"/>
+    <col min="6" max="6" width="4.5" style="23" customWidth="1"/>
+    <col min="7" max="7" width="44.1640625" style="23" customWidth="1"/>
+    <col min="8" max="8" width="2.5" style="23" customWidth="1"/>
+    <col min="9" max="9" width="42.5" style="23" customWidth="1"/>
+    <col min="10" max="10" width="3.5" style="23" customWidth="1"/>
+    <col min="11" max="16384" width="10.83203125" style="23"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="16" customHeight="1">
-      <c r="B2" s="120" t="s">
-        <v>50</v>
-      </c>
-      <c r="C2" s="121"/>
-      <c r="D2" s="121"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="121"/>
-      <c r="G2" s="122"/>
+      <c r="B2" s="136" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="137"/>
+      <c r="D2" s="137"/>
+      <c r="E2" s="137"/>
+      <c r="F2" s="137"/>
+      <c r="G2" s="138"/>
     </row>
     <row r="3" spans="2:10">
-      <c r="B3" s="123"/>
-      <c r="C3" s="124"/>
-      <c r="D3" s="124"/>
-      <c r="E3" s="124"/>
-      <c r="F3" s="124"/>
-      <c r="G3" s="125"/>
+      <c r="B3" s="139"/>
+      <c r="C3" s="140"/>
+      <c r="D3" s="140"/>
+      <c r="E3" s="140"/>
+      <c r="F3" s="140"/>
+      <c r="G3" s="141"/>
     </row>
     <row r="4" spans="2:10">
-      <c r="B4" s="123"/>
-      <c r="C4" s="124"/>
-      <c r="D4" s="124"/>
-      <c r="E4" s="124"/>
-      <c r="F4" s="124"/>
-      <c r="G4" s="125"/>
+      <c r="B4" s="139"/>
+      <c r="C4" s="140"/>
+      <c r="D4" s="140"/>
+      <c r="E4" s="140"/>
+      <c r="F4" s="140"/>
+      <c r="G4" s="141"/>
     </row>
     <row r="5" spans="2:10">
-      <c r="B5" s="126"/>
-      <c r="C5" s="127"/>
-      <c r="D5" s="127"/>
-      <c r="E5" s="127"/>
-      <c r="F5" s="127"/>
-      <c r="G5" s="128"/>
+      <c r="B5" s="142"/>
+      <c r="C5" s="143"/>
+      <c r="D5" s="143"/>
+      <c r="E5" s="143"/>
+      <c r="F5" s="143"/>
+      <c r="G5" s="144"/>
     </row>
     <row r="6" spans="2:10" ht="17" thickBot="1"/>
     <row r="7" spans="2:10">
@@ -3004,7 +2714,7 @@
     <row r="10" spans="2:10" s="9" customFormat="1" ht="17" thickBot="1">
       <c r="B10" s="14"/>
       <c r="C10" s="9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D10" s="21"/>
       <c r="J10" s="10"/>
@@ -3012,396 +2722,394 @@
     <row r="11" spans="2:10" s="9" customFormat="1" ht="17" thickBot="1">
       <c r="B11" s="14"/>
       <c r="C11" s="73" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="E11" s="22">
         <f>'Research data'!E7</f>
-        <v>2.8361075544174135</v>
+        <v>1.7630429999999999</v>
       </c>
       <c r="F11" s="26"/>
-      <c r="G11" s="77" t="s">
-        <v>49</v>
-      </c>
+      <c r="G11" s="77"/>
       <c r="H11" s="20"/>
-      <c r="I11" s="76" t="s">
-        <v>40</v>
+      <c r="I11" s="148" t="s">
+        <v>50</v>
       </c>
       <c r="J11" s="10"/>
     </row>
     <row r="12" spans="2:10" s="9" customFormat="1" ht="17" thickBot="1">
       <c r="B12" s="14"/>
-      <c r="C12" s="91" t="s">
-        <v>78</v>
+      <c r="C12" s="86" t="s">
+        <v>53</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="E12" s="97">
+        <v>54</v>
+      </c>
+      <c r="E12" s="92">
         <f>'Research data'!E8</f>
         <v>0.216</v>
       </c>
-      <c r="F12" s="91"/>
-      <c r="G12" s="91"/>
+      <c r="F12" s="86"/>
+      <c r="G12" s="86"/>
       <c r="H12" s="20"/>
-      <c r="I12" s="119" t="s">
-        <v>129</v>
+      <c r="I12" s="114" t="s">
+        <v>104</v>
       </c>
       <c r="J12" s="10"/>
     </row>
     <row r="13" spans="2:10" s="9" customFormat="1" ht="17" thickBot="1">
       <c r="B13" s="14"/>
-      <c r="C13" s="91" t="s">
-        <v>80</v>
+      <c r="C13" s="86" t="s">
+        <v>55</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="E13" s="118">
+        <v>56</v>
+      </c>
+      <c r="E13" s="113">
         <f>'Research data'!E9</f>
         <v>5.4866766968530989E-5</v>
       </c>
-      <c r="F13" s="91"/>
-      <c r="G13" s="91"/>
+      <c r="F13" s="86"/>
+      <c r="G13" s="86"/>
       <c r="H13" s="20"/>
-      <c r="I13" s="119" t="s">
-        <v>130</v>
+      <c r="I13" s="114" t="s">
+        <v>105</v>
       </c>
       <c r="J13" s="10"/>
     </row>
     <row r="14" spans="2:10" s="9" customFormat="1" ht="17" thickBot="1">
       <c r="B14" s="14"/>
-      <c r="C14" s="91" t="s">
-        <v>113</v>
+      <c r="C14" s="86" t="s">
+        <v>88</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="E14" s="97">
+        <v>60</v>
+      </c>
+      <c r="E14" s="92">
         <f>'Research data'!E10</f>
         <v>0.32</v>
       </c>
-      <c r="F14" s="91"/>
-      <c r="G14" s="91"/>
+      <c r="F14" s="86"/>
+      <c r="G14" s="86"/>
       <c r="H14" s="20"/>
-      <c r="I14" s="119" t="s">
-        <v>129</v>
+      <c r="I14" s="114" t="s">
+        <v>104</v>
       </c>
       <c r="J14" s="10"/>
     </row>
-    <row r="15" spans="2:10" s="93" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="B15" s="94"/>
-      <c r="C15" s="91" t="s">
-        <v>84</v>
+    <row r="15" spans="2:10" s="88" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="B15" s="89"/>
+      <c r="C15" s="86" t="s">
+        <v>59</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="E15" s="97">
+        <v>60</v>
+      </c>
+      <c r="E15" s="92">
         <f>'Research data'!E11</f>
         <v>0.32</v>
       </c>
-      <c r="F15" s="91"/>
-      <c r="G15" s="91"/>
-      <c r="H15" s="91"/>
-      <c r="I15" s="119" t="s">
-        <v>129</v>
-      </c>
-      <c r="J15" s="96"/>
-    </row>
-    <row r="16" spans="2:10" s="93" customFormat="1" ht="17" thickBot="1">
-      <c r="B16" s="94"/>
-      <c r="C16" s="91" t="s">
-        <v>82</v>
+      <c r="F15" s="86"/>
+      <c r="G15" s="86"/>
+      <c r="H15" s="86"/>
+      <c r="I15" s="114" t="s">
+        <v>104</v>
+      </c>
+      <c r="J15" s="91"/>
+    </row>
+    <row r="16" spans="2:10" s="88" customFormat="1" ht="17" thickBot="1">
+      <c r="B16" s="89"/>
+      <c r="C16" s="86" t="s">
+        <v>57</v>
       </c>
       <c r="D16" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E16" s="98">
+      <c r="E16" s="93">
         <v>1</v>
       </c>
-      <c r="F16" s="91"/>
-      <c r="G16" s="91"/>
-      <c r="H16" s="91"/>
-      <c r="I16" s="129" t="s">
-        <v>134</v>
-      </c>
-      <c r="J16" s="96"/>
-    </row>
-    <row r="17" spans="2:10" s="93" customFormat="1" ht="17" thickBot="1">
-      <c r="B17" s="94"/>
-      <c r="C17" s="91" t="s">
-        <v>83</v>
+      <c r="F16" s="86"/>
+      <c r="G16" s="86"/>
+      <c r="H16" s="86"/>
+      <c r="I16" s="115" t="s">
+        <v>108</v>
+      </c>
+      <c r="J16" s="91"/>
+    </row>
+    <row r="17" spans="2:10" s="88" customFormat="1" ht="17" thickBot="1">
+      <c r="B17" s="89"/>
+      <c r="C17" s="86" t="s">
+        <v>58</v>
       </c>
       <c r="D17" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E17" s="99">
+      <c r="E17" s="94">
         <v>0</v>
       </c>
-      <c r="F17" s="91"/>
-      <c r="G17" s="91"/>
-      <c r="H17" s="91"/>
-      <c r="I17" s="119" t="s">
-        <v>131</v>
-      </c>
-      <c r="J17" s="96"/>
-    </row>
-    <row r="18" spans="2:10" s="93" customFormat="1">
-      <c r="B18" s="94"/>
+      <c r="F17" s="86"/>
+      <c r="G17" s="86"/>
+      <c r="H17" s="86"/>
+      <c r="I17" s="114" t="s">
+        <v>106</v>
+      </c>
+      <c r="J17" s="91"/>
+    </row>
+    <row r="18" spans="2:10" s="88" customFormat="1">
+      <c r="B18" s="89"/>
       <c r="D18" s="55"/>
-      <c r="E18" s="100"/>
-      <c r="J18" s="96"/>
-    </row>
-    <row r="19" spans="2:10" s="93" customFormat="1" ht="17" thickBot="1">
-      <c r="B19" s="94"/>
+      <c r="E18" s="95"/>
+      <c r="J18" s="91"/>
+    </row>
+    <row r="19" spans="2:10" s="88" customFormat="1" ht="17" thickBot="1">
+      <c r="B19" s="89"/>
       <c r="C19" s="9" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="D19" s="55"/>
-      <c r="E19" s="101"/>
-      <c r="J19" s="96"/>
-    </row>
-    <row r="20" spans="2:10" s="93" customFormat="1" ht="17" thickBot="1">
-      <c r="B20" s="94"/>
-      <c r="C20" s="91" t="s">
-        <v>87</v>
+      <c r="E19" s="96"/>
+      <c r="J19" s="91"/>
+    </row>
+    <row r="20" spans="2:10" s="88" customFormat="1" ht="17" thickBot="1">
+      <c r="B20" s="89"/>
+      <c r="C20" s="86" t="s">
+        <v>62</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="E20" s="95">
+        <v>63</v>
+      </c>
+      <c r="E20" s="90">
         <v>0</v>
       </c>
-      <c r="F20" s="91"/>
-      <c r="G20" s="91" t="s">
+      <c r="F20" s="86"/>
+      <c r="G20" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="H20" s="91"/>
-      <c r="I20" s="92" t="s">
-        <v>110</v>
-      </c>
-      <c r="J20" s="96"/>
-    </row>
-    <row r="21" spans="2:10" s="93" customFormat="1" ht="17" thickBot="1">
-      <c r="B21" s="94"/>
-      <c r="C21" s="91" t="s">
-        <v>89</v>
+      <c r="H20" s="86"/>
+      <c r="I20" s="87" t="s">
+        <v>85</v>
+      </c>
+      <c r="J20" s="91"/>
+    </row>
+    <row r="21" spans="2:10" s="88" customFormat="1" ht="17" thickBot="1">
+      <c r="B21" s="89"/>
+      <c r="C21" s="86" t="s">
+        <v>64</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E21" s="95">
+        <v>65</v>
+      </c>
+      <c r="E21" s="90">
         <v>0</v>
       </c>
-      <c r="F21" s="91"/>
-      <c r="G21" s="91" t="s">
-        <v>91</v>
-      </c>
-      <c r="H21" s="91"/>
-      <c r="I21" s="92" t="s">
-        <v>110</v>
-      </c>
-      <c r="J21" s="96"/>
-    </row>
-    <row r="22" spans="2:10" s="93" customFormat="1" ht="17" thickBot="1">
-      <c r="B22" s="102"/>
-      <c r="C22" s="103" t="s">
-        <v>92</v>
-      </c>
-      <c r="D22" s="104"/>
-      <c r="E22" s="95">
+      <c r="F21" s="86"/>
+      <c r="G21" s="86" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21" s="86"/>
+      <c r="I21" s="87" t="s">
+        <v>85</v>
+      </c>
+      <c r="J21" s="91"/>
+    </row>
+    <row r="22" spans="2:10" s="88" customFormat="1" ht="17" thickBot="1">
+      <c r="B22" s="97"/>
+      <c r="C22" s="98" t="s">
+        <v>67</v>
+      </c>
+      <c r="D22" s="99"/>
+      <c r="E22" s="90">
         <v>0</v>
       </c>
-      <c r="F22" s="103"/>
-      <c r="G22" s="103" t="s">
-        <v>93</v>
-      </c>
-      <c r="H22" s="103"/>
-      <c r="I22" s="92" t="s">
-        <v>110</v>
-      </c>
-      <c r="J22" s="105"/>
-    </row>
-    <row r="23" spans="2:10" s="93" customFormat="1" ht="17" thickBot="1">
-      <c r="B23" s="102"/>
-      <c r="C23" s="103" t="s">
-        <v>94</v>
-      </c>
-      <c r="D23" s="104"/>
-      <c r="E23" s="95">
+      <c r="F22" s="98"/>
+      <c r="G22" s="98" t="s">
+        <v>68</v>
+      </c>
+      <c r="H22" s="98"/>
+      <c r="I22" s="87" t="s">
+        <v>85</v>
+      </c>
+      <c r="J22" s="100"/>
+    </row>
+    <row r="23" spans="2:10" s="88" customFormat="1" ht="17" thickBot="1">
+      <c r="B23" s="97"/>
+      <c r="C23" s="98" t="s">
+        <v>69</v>
+      </c>
+      <c r="D23" s="99"/>
+      <c r="E23" s="90">
         <v>0</v>
       </c>
-      <c r="F23" s="103"/>
-      <c r="G23" s="103" t="s">
-        <v>95</v>
-      </c>
-      <c r="H23" s="103"/>
-      <c r="I23" s="92" t="s">
-        <v>110</v>
-      </c>
-      <c r="J23" s="105"/>
-    </row>
-    <row r="24" spans="2:10" s="93" customFormat="1" ht="17" thickBot="1">
-      <c r="B24" s="102"/>
-      <c r="C24" s="103" t="s">
-        <v>96</v>
-      </c>
-      <c r="D24" s="104"/>
-      <c r="E24" s="95">
+      <c r="F23" s="98"/>
+      <c r="G23" s="98" t="s">
+        <v>70</v>
+      </c>
+      <c r="H23" s="98"/>
+      <c r="I23" s="87" t="s">
+        <v>85</v>
+      </c>
+      <c r="J23" s="100"/>
+    </row>
+    <row r="24" spans="2:10" s="88" customFormat="1" ht="17" thickBot="1">
+      <c r="B24" s="97"/>
+      <c r="C24" s="98" t="s">
+        <v>71</v>
+      </c>
+      <c r="D24" s="99"/>
+      <c r="E24" s="90">
         <v>0</v>
       </c>
-      <c r="F24" s="103"/>
-      <c r="G24" s="103" t="s">
-        <v>97</v>
-      </c>
-      <c r="H24" s="103"/>
-      <c r="I24" s="92" t="s">
-        <v>110</v>
-      </c>
-      <c r="J24" s="105"/>
-    </row>
-    <row r="25" spans="2:10" s="93" customFormat="1" ht="17" thickBot="1">
-      <c r="B25" s="102"/>
-      <c r="C25" s="103" t="s">
-        <v>98</v>
-      </c>
-      <c r="D25" s="104"/>
-      <c r="E25" s="95">
+      <c r="F24" s="98"/>
+      <c r="G24" s="98" t="s">
+        <v>72</v>
+      </c>
+      <c r="H24" s="98"/>
+      <c r="I24" s="87" t="s">
+        <v>85</v>
+      </c>
+      <c r="J24" s="100"/>
+    </row>
+    <row r="25" spans="2:10" s="88" customFormat="1" ht="17" thickBot="1">
+      <c r="B25" s="97"/>
+      <c r="C25" s="98" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" s="99"/>
+      <c r="E25" s="90">
         <v>0</v>
       </c>
-      <c r="F25" s="103"/>
-      <c r="G25" s="91" t="s">
-        <v>99</v>
-      </c>
-      <c r="H25" s="103"/>
-      <c r="I25" s="92" t="s">
-        <v>110</v>
-      </c>
-      <c r="J25" s="105"/>
-    </row>
-    <row r="26" spans="2:10" s="93" customFormat="1" ht="17" thickBot="1">
-      <c r="B26" s="102"/>
-      <c r="C26" s="103" t="s">
-        <v>100</v>
-      </c>
-      <c r="D26" s="104"/>
-      <c r="E26" s="95">
+      <c r="F25" s="98"/>
+      <c r="G25" s="86" t="s">
+        <v>74</v>
+      </c>
+      <c r="H25" s="98"/>
+      <c r="I25" s="87" t="s">
+        <v>85</v>
+      </c>
+      <c r="J25" s="100"/>
+    </row>
+    <row r="26" spans="2:10" s="88" customFormat="1" ht="17" thickBot="1">
+      <c r="B26" s="97"/>
+      <c r="C26" s="98" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="99"/>
+      <c r="E26" s="90">
         <v>0</v>
       </c>
-      <c r="F26" s="103"/>
-      <c r="G26" s="91" t="s">
-        <v>101</v>
-      </c>
-      <c r="H26" s="103"/>
-      <c r="I26" s="92" t="s">
-        <v>110</v>
-      </c>
-      <c r="J26" s="105"/>
-    </row>
-    <row r="27" spans="2:10" s="93" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="B27" s="94"/>
-      <c r="C27" s="91" t="s">
-        <v>102</v>
+      <c r="F26" s="98"/>
+      <c r="G26" s="86" t="s">
+        <v>76</v>
+      </c>
+      <c r="H26" s="98"/>
+      <c r="I26" s="87" t="s">
+        <v>85</v>
+      </c>
+      <c r="J26" s="100"/>
+    </row>
+    <row r="27" spans="2:10" s="88" customFormat="1" ht="15" customHeight="1" thickBot="1">
+      <c r="B27" s="89"/>
+      <c r="C27" s="86" t="s">
+        <v>77</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="E27" s="106">
+        <v>78</v>
+      </c>
+      <c r="E27" s="101">
         <v>0.04</v>
       </c>
-      <c r="F27" s="91"/>
-      <c r="G27" s="130" t="s">
-        <v>138</v>
-      </c>
-      <c r="H27" s="91"/>
-      <c r="I27" s="110" t="s">
-        <v>139</v>
-      </c>
-      <c r="J27" s="96"/>
-    </row>
-    <row r="28" spans="2:10" s="93" customFormat="1" ht="17" thickBot="1">
-      <c r="B28" s="94"/>
-      <c r="C28" s="91" t="s">
-        <v>104</v>
+      <c r="F27" s="86"/>
+      <c r="G27" s="116" t="s">
+        <v>112</v>
+      </c>
+      <c r="H27" s="86"/>
+      <c r="I27" s="105" t="s">
+        <v>113</v>
+      </c>
+      <c r="J27" s="91"/>
+    </row>
+    <row r="28" spans="2:10" s="88" customFormat="1" ht="17" thickBot="1">
+      <c r="B28" s="89"/>
+      <c r="C28" s="86" t="s">
+        <v>79</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="E28" s="95">
+        <v>80</v>
+      </c>
+      <c r="E28" s="90">
         <v>0</v>
       </c>
-      <c r="F28" s="91"/>
-      <c r="G28" s="91"/>
-      <c r="H28" s="91"/>
-      <c r="I28" s="92" t="s">
-        <v>109</v>
-      </c>
-      <c r="J28" s="96"/>
-    </row>
-    <row r="29" spans="2:10" s="93" customFormat="1">
-      <c r="B29" s="94"/>
-      <c r="C29" s="91"/>
+      <c r="F28" s="86"/>
+      <c r="G28" s="86"/>
+      <c r="H28" s="86"/>
+      <c r="I28" s="87" t="s">
+        <v>84</v>
+      </c>
+      <c r="J28" s="91"/>
+    </row>
+    <row r="29" spans="2:10" s="88" customFormat="1">
+      <c r="B29" s="89"/>
+      <c r="C29" s="86"/>
       <c r="D29" s="13"/>
-      <c r="E29" s="84"/>
-      <c r="F29" s="91"/>
-      <c r="G29" s="91"/>
-      <c r="H29" s="91"/>
-      <c r="J29" s="96"/>
-    </row>
-    <row r="30" spans="2:10" s="93" customFormat="1" ht="17" thickBot="1">
-      <c r="B30" s="94"/>
+      <c r="E29" s="81"/>
+      <c r="F29" s="86"/>
+      <c r="G29" s="86"/>
+      <c r="H29" s="86"/>
+      <c r="J29" s="91"/>
+    </row>
+    <row r="30" spans="2:10" s="88" customFormat="1" ht="17" thickBot="1">
+      <c r="B30" s="89"/>
       <c r="C30" s="9" t="s">
         <v>4</v>
       </c>
       <c r="D30" s="55"/>
-      <c r="E30" s="84"/>
-      <c r="J30" s="96"/>
-    </row>
-    <row r="31" spans="2:10" s="93" customFormat="1" ht="17" thickBot="1">
-      <c r="B31" s="94"/>
-      <c r="C31" s="91" t="s">
-        <v>106</v>
+      <c r="E30" s="81"/>
+      <c r="J30" s="91"/>
+    </row>
+    <row r="31" spans="2:10" s="88" customFormat="1" ht="17" thickBot="1">
+      <c r="B31" s="89"/>
+      <c r="C31" s="86" t="s">
+        <v>81</v>
       </c>
       <c r="D31" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="E31" s="99">
+        <v>82</v>
+      </c>
+      <c r="E31" s="94">
         <f>'Research data'!E14</f>
         <v>14</v>
       </c>
-      <c r="F31" s="91"/>
-      <c r="G31" s="91" t="s">
-        <v>108</v>
-      </c>
-      <c r="H31" s="91"/>
+      <c r="F31" s="86"/>
+      <c r="G31" s="86" t="s">
+        <v>83</v>
+      </c>
+      <c r="H31" s="86"/>
       <c r="I31" s="76" t="s">
-        <v>40</v>
-      </c>
-      <c r="J31" s="96"/>
-    </row>
-    <row r="32" spans="2:10" s="93" customFormat="1" ht="17" thickBot="1">
-      <c r="B32" s="94"/>
-      <c r="C32" s="130" t="s">
-        <v>135</v>
+        <v>39</v>
+      </c>
+      <c r="J31" s="91"/>
+    </row>
+    <row r="32" spans="2:10" s="88" customFormat="1" ht="17" thickBot="1">
+      <c r="B32" s="89"/>
+      <c r="C32" s="116" t="s">
+        <v>109</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="E32" s="98">
+        <v>82</v>
+      </c>
+      <c r="E32" s="93">
         <v>0</v>
       </c>
-      <c r="F32" s="91"/>
-      <c r="G32" s="130" t="s">
-        <v>136</v>
-      </c>
-      <c r="H32" s="91"/>
-      <c r="I32" s="129" t="s">
-        <v>137</v>
-      </c>
-      <c r="J32" s="96"/>
+      <c r="F32" s="86"/>
+      <c r="G32" s="116" t="s">
+        <v>110</v>
+      </c>
+      <c r="H32" s="86"/>
+      <c r="I32" s="115" t="s">
+        <v>111</v>
+      </c>
+      <c r="J32" s="91"/>
     </row>
     <row r="33" spans="2:10" ht="17" thickBot="1">
       <c r="B33" s="27"/>
@@ -3417,8 +3125,8 @@
       <c r="F33" s="26"/>
       <c r="G33" s="26"/>
       <c r="H33" s="26"/>
-      <c r="I33" s="129" t="s">
-        <v>134</v>
+      <c r="I33" s="115" t="s">
+        <v>108</v>
       </c>
       <c r="J33" s="56"/>
     </row>
@@ -3448,23 +3156,23 @@
   <sheetPr codeName="Sheet3">
     <tabColor theme="6" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A2:L17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
+  <dimension ref="B2:L15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="2" width="4.42578125" style="32" customWidth="1"/>
-    <col min="3" max="3" width="33.140625" style="32" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" style="32" customWidth="1"/>
-    <col min="5" max="5" width="9.42578125" style="32" customWidth="1"/>
-    <col min="6" max="6" width="2.42578125" style="32" customWidth="1"/>
-    <col min="7" max="7" width="2.140625" style="32" customWidth="1"/>
-    <col min="8" max="10" width="17.140625" style="32" customWidth="1"/>
-    <col min="11" max="11" width="2.85546875" style="32" customWidth="1"/>
-    <col min="12" max="12" width="59.140625" style="32" customWidth="1"/>
-    <col min="13" max="16384" width="10.85546875" style="32"/>
+    <col min="1" max="2" width="4.5" style="32" customWidth="1"/>
+    <col min="3" max="3" width="33.1640625" style="32" customWidth="1"/>
+    <col min="4" max="4" width="11.5" style="32" customWidth="1"/>
+    <col min="5" max="5" width="9.5" style="32" customWidth="1"/>
+    <col min="6" max="6" width="2.5" style="32" customWidth="1"/>
+    <col min="7" max="7" width="2.1640625" style="32" customWidth="1"/>
+    <col min="8" max="10" width="17.1640625" style="32" customWidth="1"/>
+    <col min="11" max="11" width="7.1640625" style="32" customWidth="1"/>
+    <col min="12" max="12" width="59.1640625" style="32" customWidth="1"/>
+    <col min="13" max="16384" width="10.83203125" style="32"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:12" ht="17" thickBot="1"/>
-    <row r="3" spans="1:12">
+    <row r="2" spans="2:12" ht="17" thickBot="1"/>
+    <row r="3" spans="2:12">
       <c r="B3" s="33"/>
       <c r="C3" s="34"/>
       <c r="D3" s="34"/>
@@ -3475,249 +3183,192 @@
       <c r="I3" s="34"/>
       <c r="J3" s="34"/>
       <c r="K3" s="34"/>
-      <c r="L3" s="132"/>
-    </row>
-    <row r="4" spans="1:12" s="9" customFormat="1">
+      <c r="L3" s="117"/>
+    </row>
+    <row r="4" spans="2:12" s="9" customFormat="1">
       <c r="B4" s="14"/>
       <c r="C4" s="57" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" s="57" t="s">
         <v>8</v>
       </c>
       <c r="E4" s="57" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F4" s="57"/>
       <c r="G4" s="57"/>
       <c r="H4" s="57" t="s">
+        <v>39</v>
+      </c>
+      <c r="I4" s="57" t="s">
+        <v>104</v>
+      </c>
+      <c r="J4" s="57" t="s">
+        <v>105</v>
+      </c>
+      <c r="K4" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="L4" s="118" t="s">
         <v>40</v>
       </c>
-      <c r="I4" s="57" t="s">
-        <v>129</v>
-      </c>
-      <c r="J4" s="57" t="s">
-        <v>130</v>
-      </c>
-      <c r="K4" s="57"/>
-      <c r="L4" s="133" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="18" customHeight="1">
+    </row>
+    <row r="5" spans="2:12" ht="18" customHeight="1">
       <c r="B5" s="35"/>
-      <c r="C5" s="134"/>
-      <c r="D5" s="131"/>
-      <c r="E5" s="135"/>
-      <c r="F5" s="135"/>
-      <c r="G5" s="131"/>
-      <c r="H5" s="131"/>
-      <c r="I5" s="131"/>
-      <c r="J5" s="131"/>
-      <c r="K5" s="131"/>
-      <c r="L5" s="136"/>
-    </row>
-    <row r="6" spans="1:12" ht="18" customHeight="1" thickBot="1">
+      <c r="C5" s="119"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="120"/>
+      <c r="L5" s="121"/>
+    </row>
+    <row r="6" spans="2:12" ht="18" customHeight="1" thickBot="1">
       <c r="B6" s="35"/>
-      <c r="C6" s="137" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="137"/>
-      <c r="E6" s="138"/>
-      <c r="F6" s="138"/>
-      <c r="G6" s="131"/>
-      <c r="H6" s="131"/>
-      <c r="I6" s="131"/>
-      <c r="J6" s="131"/>
-      <c r="K6" s="131"/>
-      <c r="L6" s="139"/>
-    </row>
-    <row r="7" spans="1:12" ht="17" thickBot="1">
+      <c r="C6" s="122" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="122"/>
+      <c r="E6" s="123"/>
+      <c r="F6" s="123"/>
+      <c r="L6" s="124"/>
+    </row>
+    <row r="7" spans="2:12" ht="17" thickBot="1">
       <c r="B7" s="35"/>
-      <c r="C7" s="140" t="s">
-        <v>76</v>
-      </c>
-      <c r="D7" s="141" t="s">
-        <v>77</v>
+      <c r="C7" s="125" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="126" t="s">
+        <v>52</v>
       </c>
       <c r="E7" s="75">
-        <f>H7</f>
-        <v>2.8361075544174135</v>
-      </c>
-      <c r="F7" s="135"/>
-      <c r="G7" s="131"/>
-      <c r="H7" s="75">
-        <f>Notes!E34</f>
-        <v>2.8361075544174135</v>
-      </c>
-      <c r="I7" s="131"/>
-      <c r="J7" s="131"/>
-      <c r="K7" s="131"/>
-      <c r="L7" s="142"/>
-    </row>
-    <row r="8" spans="1:12" ht="17" thickBot="1">
+        <f>K7</f>
+        <v>1.7630429999999999</v>
+      </c>
+      <c r="F7" s="120"/>
+      <c r="K7" s="75">
+        <f>Notes!E17</f>
+        <v>1.7630429999999999</v>
+      </c>
+      <c r="L7" s="127"/>
+    </row>
+    <row r="8" spans="2:12" ht="17" thickBot="1">
       <c r="B8" s="35"/>
-      <c r="C8" s="143" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" s="144" t="s">
-        <v>79</v>
+      <c r="C8" s="86" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="E8" s="75">
         <f>I8</f>
         <v>0.216</v>
       </c>
-      <c r="F8" s="135"/>
-      <c r="G8" s="131"/>
-      <c r="H8" s="131"/>
-      <c r="I8" s="107">
+      <c r="F8" s="120"/>
+      <c r="I8" s="102">
         <f>Notes!E108</f>
         <v>0.216</v>
       </c>
-      <c r="J8" s="145"/>
-      <c r="K8" s="131"/>
-      <c r="L8" s="136"/>
-    </row>
-    <row r="9" spans="1:12" ht="17" thickBot="1">
+      <c r="J8" s="128"/>
+      <c r="L8" s="121"/>
+    </row>
+    <row r="9" spans="2:12" ht="17" thickBot="1">
       <c r="B9" s="35"/>
-      <c r="C9" s="143" t="s">
-        <v>80</v>
-      </c>
-      <c r="D9" s="144" t="s">
-        <v>81</v>
+      <c r="C9" s="86" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>56</v>
       </c>
       <c r="E9" s="75">
         <f>J9</f>
         <v>5.4866766968530989E-5</v>
       </c>
-      <c r="F9" s="131"/>
-      <c r="G9" s="131"/>
-      <c r="H9" s="131"/>
-      <c r="I9" s="145"/>
-      <c r="J9" s="107">
+      <c r="I9" s="128"/>
+      <c r="J9" s="102">
         <f>Notes!E132</f>
         <v>5.4866766968530989E-5</v>
       </c>
-      <c r="K9" s="131"/>
-      <c r="L9" s="146"/>
-    </row>
-    <row r="10" spans="1:12" ht="17" thickBot="1">
+      <c r="L9" s="129"/>
+    </row>
+    <row r="10" spans="2:12" ht="17" thickBot="1">
       <c r="B10" s="35"/>
-      <c r="C10" s="143" t="s">
-        <v>113</v>
-      </c>
-      <c r="D10" s="144" t="s">
-        <v>85</v>
+      <c r="C10" s="86" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>60</v>
       </c>
       <c r="E10" s="75">
         <f t="shared" ref="E10:E11" si="0">I10</f>
         <v>0.32</v>
       </c>
-      <c r="F10" s="131"/>
-      <c r="G10" s="131"/>
-      <c r="H10" s="131"/>
-      <c r="I10" s="107">
+      <c r="I10" s="102">
         <f>Notes!E111</f>
         <v>0.32</v>
       </c>
-      <c r="J10" s="145"/>
-      <c r="K10" s="131"/>
-      <c r="L10" s="146"/>
-    </row>
-    <row r="11" spans="1:12" ht="17" thickBot="1">
+      <c r="J10" s="128"/>
+      <c r="L10" s="129"/>
+    </row>
+    <row r="11" spans="2:12" ht="17" thickBot="1">
       <c r="B11" s="35"/>
-      <c r="C11" s="147" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" s="144" t="s">
-        <v>85</v>
+      <c r="C11" s="130" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>60</v>
       </c>
       <c r="E11" s="75">
         <f t="shared" si="0"/>
         <v>0.32</v>
       </c>
-      <c r="F11" s="131"/>
-      <c r="G11" s="131"/>
-      <c r="H11" s="131"/>
-      <c r="I11" s="107">
+      <c r="I11" s="102">
         <f>Notes!E110</f>
         <v>0.32</v>
       </c>
-      <c r="J11" s="145"/>
-      <c r="K11" s="131"/>
-      <c r="L11" s="146"/>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="J11" s="128"/>
+      <c r="L11" s="129"/>
+    </row>
+    <row r="12" spans="2:12">
       <c r="B12" s="35"/>
-      <c r="C12" s="131"/>
-      <c r="D12" s="131"/>
-      <c r="E12" s="131"/>
-      <c r="F12" s="131"/>
-      <c r="G12" s="131"/>
-      <c r="H12" s="131"/>
-      <c r="I12" s="131"/>
-      <c r="J12" s="131"/>
-      <c r="K12" s="131"/>
-      <c r="L12" s="146"/>
-    </row>
-    <row r="13" spans="1:12" ht="17" thickBot="1">
+      <c r="L12" s="129"/>
+    </row>
+    <row r="13" spans="2:12" ht="17" thickBot="1">
       <c r="B13" s="35"/>
-      <c r="C13" s="148" t="s">
+      <c r="C13" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="D13" s="149"/>
-      <c r="E13" s="131"/>
-      <c r="F13" s="131"/>
-      <c r="G13" s="131"/>
-      <c r="H13" s="131"/>
-      <c r="I13" s="131"/>
-      <c r="J13" s="131"/>
-      <c r="K13" s="131"/>
-      <c r="L13" s="146"/>
-    </row>
-    <row r="14" spans="1:12" ht="17" thickBot="1">
+      <c r="D13" s="55"/>
+      <c r="L13" s="129"/>
+    </row>
+    <row r="14" spans="2:12" ht="17" thickBot="1">
       <c r="B14" s="35"/>
-      <c r="C14" s="143" t="s">
-        <v>106</v>
-      </c>
-      <c r="D14" s="144" t="s">
-        <v>107</v>
+      <c r="C14" s="86" t="s">
+        <v>81</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>82</v>
       </c>
       <c r="E14" s="75">
         <f>H14</f>
         <v>14</v>
       </c>
-      <c r="F14" s="131"/>
-      <c r="G14" s="131"/>
       <c r="H14" s="75">
         <f>Notes!C89</f>
         <v>14</v>
       </c>
-      <c r="I14" s="131"/>
-      <c r="J14" s="131"/>
-      <c r="K14" s="131"/>
-      <c r="L14" s="146"/>
-    </row>
-    <row r="15" spans="1:12" ht="17" thickBot="1">
-      <c r="B15" s="150"/>
-      <c r="C15" s="151"/>
-      <c r="D15" s="151"/>
-      <c r="E15" s="151"/>
-      <c r="F15" s="151"/>
-      <c r="G15" s="151"/>
-      <c r="H15" s="151"/>
-      <c r="I15" s="151"/>
-      <c r="J15" s="151"/>
-      <c r="K15" s="151"/>
-      <c r="L15" s="152"/>
-    </row>
-    <row r="16" spans="1:12">
-      <c r="A16" s="131"/>
-      <c r="B16" s="131"/>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="131"/>
-      <c r="B17" s="131"/>
+      <c r="L14" s="129"/>
+    </row>
+    <row r="15" spans="2:12" ht="17" thickBot="1">
+      <c r="B15" s="131"/>
+      <c r="C15" s="132"/>
+      <c r="D15" s="132"/>
+      <c r="E15" s="132"/>
+      <c r="F15" s="132"/>
+      <c r="G15" s="132"/>
+      <c r="H15" s="132"/>
+      <c r="I15" s="132"/>
+      <c r="J15" s="132"/>
+      <c r="K15" s="132"/>
+      <c r="L15" s="133"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3731,18 +3382,18 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="B1:J41"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="33.140625" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="33.1640625" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="3.140625" style="58" customWidth="1"/>
+    <col min="1" max="1" width="3.1640625" style="58" customWidth="1"/>
     <col min="2" max="2" width="4" style="58" customWidth="1"/>
-    <col min="3" max="3" width="47.28515625" style="58" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" style="58" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" style="58" customWidth="1"/>
-    <col min="6" max="7" width="13.140625" style="58" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" style="59" customWidth="1"/>
-    <col min="9" max="9" width="32.42578125" style="59" customWidth="1"/>
-    <col min="10" max="10" width="98.42578125" style="58" customWidth="1"/>
-    <col min="11" max="16384" width="33.140625" style="58"/>
+    <col min="3" max="3" width="47.33203125" style="58" customWidth="1"/>
+    <col min="4" max="4" width="16.1640625" style="58" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" style="58" customWidth="1"/>
+    <col min="6" max="7" width="13.1640625" style="58" customWidth="1"/>
+    <col min="8" max="8" width="12.5" style="59" customWidth="1"/>
+    <col min="9" max="9" width="32.5" style="59" customWidth="1"/>
+    <col min="10" max="10" width="98.5" style="58" customWidth="1"/>
+    <col min="11" max="16384" width="33.1640625" style="58"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="17" thickBot="1"/>
@@ -3787,13 +3438,13 @@
         <v>17</v>
       </c>
       <c r="G5" s="52" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H5" s="66" t="s">
         <v>18</v>
       </c>
       <c r="I5" s="66" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J5" s="52" t="s">
         <v>9</v>
@@ -3802,26 +3453,26 @@
     <row r="6" spans="2:10">
       <c r="B6" s="63"/>
       <c r="C6" s="78" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="58" t="s">
-        <v>40</v>
+        <v>46</v>
+      </c>
+      <c r="D6" s="147" t="s">
+        <v>118</v>
       </c>
       <c r="E6" s="58" t="s">
         <v>6</v>
       </c>
       <c r="F6" s="58">
-        <v>2013</v>
+        <v>2024</v>
       </c>
       <c r="G6" s="58">
-        <v>2012</v>
-      </c>
-      <c r="H6" s="58"/>
-      <c r="I6" s="72" t="s">
-        <v>45</v>
-      </c>
-      <c r="J6" s="58" t="s">
-        <v>21</v>
+        <v>2024</v>
+      </c>
+      <c r="H6" s="58">
+        <v>2026</v>
+      </c>
+      <c r="I6" s="72"/>
+      <c r="J6" s="145" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="2:10">
@@ -3842,170 +3493,124 @@
     </row>
     <row r="9" spans="2:10">
       <c r="B9" s="63"/>
-    </row>
-    <row r="10" spans="2:10" s="86" customFormat="1">
+      <c r="C9" s="146" t="s">
+        <v>48</v>
+      </c>
+      <c r="D9" s="145" t="s">
+        <v>118</v>
+      </c>
+      <c r="E9" s="145" t="s">
+        <v>6</v>
+      </c>
+      <c r="F9" s="58">
+        <v>2024</v>
+      </c>
+      <c r="G9" s="58">
+        <v>2024</v>
+      </c>
+      <c r="H9" s="58">
+        <v>2026</v>
+      </c>
+      <c r="I9" s="72"/>
+      <c r="J9" s="145" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" s="83" customFormat="1">
       <c r="B10" s="63"/>
-      <c r="C10" s="87"/>
-      <c r="H10" s="88"/>
-      <c r="I10" s="88"/>
-    </row>
-    <row r="11" spans="2:10" s="86" customFormat="1">
+      <c r="C10" s="85"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="85"/>
+      <c r="F10" s="58"/>
+      <c r="G10" s="58"/>
+      <c r="H10" s="84"/>
+      <c r="I10" s="58"/>
+      <c r="J10" s="58"/>
+    </row>
+    <row r="11" spans="2:10" s="83" customFormat="1">
       <c r="B11" s="63"/>
-      <c r="C11" s="87" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" s="86" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" s="86" t="s">
-        <v>6</v>
-      </c>
-      <c r="G11" s="86">
-        <v>2015</v>
-      </c>
-      <c r="H11" s="88" t="s">
-        <v>52</v>
-      </c>
-      <c r="I11" s="88"/>
-      <c r="J11" s="86" t="s">
-        <v>56</v>
-      </c>
+      <c r="C11" s="58"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="59"/>
+      <c r="J11" s="58"/>
     </row>
     <row r="12" spans="2:10">
       <c r="B12" s="63"/>
-      <c r="C12" s="86" t="s">
-        <v>58</v>
-      </c>
-      <c r="D12" s="86" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" s="86" t="s">
-        <v>6</v>
-      </c>
-      <c r="G12" s="58">
-        <v>2015</v>
-      </c>
-      <c r="H12" s="88" t="s">
-        <v>52</v>
-      </c>
-      <c r="J12" s="79" t="s">
-        <v>59</v>
-      </c>
     </row>
     <row r="13" spans="2:10">
       <c r="B13" s="63"/>
-      <c r="C13" s="90" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" s="90" t="s">
+      <c r="C13" s="110" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="90" t="s">
-        <v>6</v>
-      </c>
-      <c r="G13" s="58">
-        <v>2015</v>
-      </c>
-      <c r="H13" s="89" t="s">
-        <v>52</v>
-      </c>
-      <c r="J13" s="58" t="s">
-        <v>67</v>
+      <c r="D13" s="103" t="s">
+        <v>94</v>
+      </c>
+      <c r="E13" s="103" t="s">
+        <v>98</v>
+      </c>
+      <c r="F13" s="103">
+        <v>2013</v>
+      </c>
+      <c r="G13" s="103">
+        <v>2013</v>
+      </c>
+      <c r="H13" s="111" t="s">
+        <v>99</v>
+      </c>
+      <c r="I13" s="112"/>
+      <c r="J13" s="103" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="14" spans="2:10">
       <c r="B14" s="63"/>
-      <c r="C14" s="90" t="s">
-        <v>73</v>
-      </c>
-      <c r="D14" s="90" t="s">
-        <v>71</v>
-      </c>
-      <c r="E14" s="90" t="s">
-        <v>6</v>
-      </c>
-      <c r="G14" s="58">
-        <v>2014</v>
-      </c>
-      <c r="H14" s="89" t="s">
-        <v>52</v>
-      </c>
-      <c r="I14" s="58" t="s">
-        <v>74</v>
-      </c>
-      <c r="J14" s="58" t="s">
-        <v>75</v>
-      </c>
     </row>
     <row r="15" spans="2:10">
       <c r="B15" s="63"/>
+      <c r="C15" s="103" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="103" t="s">
+        <v>101</v>
+      </c>
+      <c r="E15" s="103" t="s">
+        <v>6</v>
+      </c>
+      <c r="F15" s="58">
+        <v>2019</v>
+      </c>
+      <c r="G15" s="58">
+        <v>2019</v>
+      </c>
+      <c r="H15" s="112" t="s">
+        <v>102</v>
+      </c>
+      <c r="I15" s="59" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="16" spans="2:10">
       <c r="B16" s="63"/>
-    </row>
-    <row r="17" spans="2:10" s="108" customFormat="1">
+      <c r="C16" s="103" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" s="103" customFormat="1">
       <c r="B17" s="63"/>
-      <c r="C17" s="115" t="s">
-        <v>80</v>
-      </c>
-      <c r="D17" s="108" t="s">
-        <v>119</v>
-      </c>
-      <c r="E17" s="108" t="s">
-        <v>123</v>
-      </c>
-      <c r="F17" s="108">
-        <v>2013</v>
-      </c>
-      <c r="G17" s="108">
-        <v>2013</v>
-      </c>
-      <c r="H17" s="116" t="s">
-        <v>124</v>
-      </c>
-      <c r="I17" s="117"/>
-      <c r="J17" s="108" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10">
-      <c r="B18" s="63"/>
-    </row>
-    <row r="19" spans="2:10">
-      <c r="B19" s="63"/>
-      <c r="C19" s="108" t="s">
-        <v>78</v>
-      </c>
-      <c r="D19" s="108" t="s">
-        <v>126</v>
-      </c>
-      <c r="E19" s="108" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" s="58">
-        <v>2019</v>
-      </c>
-      <c r="G19" s="58">
-        <v>2019</v>
-      </c>
-      <c r="H19" s="117" t="s">
-        <v>127</v>
-      </c>
-      <c r="I19" s="59" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10">
-      <c r="B20" s="63"/>
-      <c r="C20" s="108" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10">
-      <c r="B21" s="63"/>
-      <c r="C21" s="108" t="s">
-        <v>113</v>
-      </c>
+      <c r="C17" s="103" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="59"/>
+      <c r="I17" s="59"/>
+      <c r="J17" s="58"/>
     </row>
     <row r="22" spans="2:10">
       <c r="B22" s="63"/>
@@ -4076,18 +3681,18 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:AC174"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="16"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="5.42578125" style="68" customWidth="1"/>
-    <col min="2" max="2" width="4.42578125" style="68" customWidth="1"/>
-    <col min="3" max="3" width="12.42578125" style="68" customWidth="1"/>
-    <col min="4" max="4" width="25.140625" style="68" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" style="68" customWidth="1"/>
-    <col min="6" max="8" width="10.85546875" style="68"/>
-    <col min="9" max="9" width="20.85546875" style="68" customWidth="1"/>
-    <col min="10" max="10" width="10.85546875" style="68"/>
+    <col min="1" max="1" width="5.5" style="68" customWidth="1"/>
+    <col min="2" max="2" width="4.5" style="68" customWidth="1"/>
+    <col min="3" max="3" width="12.5" style="68" customWidth="1"/>
+    <col min="4" max="4" width="25.1640625" style="68" customWidth="1"/>
+    <col min="5" max="5" width="17.5" style="68" customWidth="1"/>
+    <col min="6" max="8" width="10.83203125" style="68"/>
+    <col min="9" max="9" width="20.83203125" style="68" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" style="68"/>
     <col min="11" max="11" width="10" style="68" customWidth="1"/>
-    <col min="12" max="16384" width="10.85546875" style="68"/>
+    <col min="12" max="16384" width="10.83203125" style="68"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:29" ht="17" thickBot="1"/>
@@ -4124,10 +3729,10 @@
     <row r="3" spans="2:29" s="9" customFormat="1">
       <c r="B3" s="51"/>
       <c r="C3" s="52" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" s="52" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E3" s="52"/>
       <c r="F3" s="52"/>
@@ -4160,27 +3765,27 @@
     </row>
     <row r="11" spans="2:29">
       <c r="B11" s="71"/>
-      <c r="C11" s="74" t="s">
-        <v>40</v>
+      <c r="C11" s="147" t="s">
+        <v>120</v>
       </c>
       <c r="E11" s="68">
-        <v>5</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="F11" s="74" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="2:29">
       <c r="B12" s="71"/>
-      <c r="C12" s="74" t="s">
-        <v>48</v>
+      <c r="C12" s="145" t="s">
+        <v>116</v>
       </c>
       <c r="E12" s="68">
         <f>1/E11</f>
-        <v>0.2</v>
+        <v>0.21739130434782611</v>
       </c>
       <c r="F12" s="74" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="2:29">
@@ -4188,252 +3793,190 @@
     </row>
     <row r="14" spans="2:29">
       <c r="B14" s="71"/>
+      <c r="C14" s="147" t="s">
+        <v>120</v>
+      </c>
+      <c r="D14" s="80"/>
+      <c r="E14" s="82">
+        <v>8.11</v>
+      </c>
+      <c r="F14" s="80" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14" s="80"/>
     </row>
     <row r="15" spans="2:29">
       <c r="B15" s="71"/>
+      <c r="C15" s="80" t="s">
+        <v>117</v>
+      </c>
+      <c r="D15" s="80"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="80"/>
+      <c r="G15" s="80"/>
     </row>
     <row r="16" spans="2:29">
       <c r="B16" s="71"/>
-    </row>
-    <row r="17" spans="2:10">
+      <c r="D16" s="145"/>
+    </row>
+    <row r="17" spans="2:9">
       <c r="B17" s="71"/>
-    </row>
-    <row r="18" spans="2:10">
-      <c r="B18" s="71"/>
-    </row>
-    <row r="19" spans="2:10">
-      <c r="B19" s="71"/>
-    </row>
-    <row r="20" spans="2:10">
-      <c r="B20" s="71"/>
-    </row>
-    <row r="21" spans="2:10">
-      <c r="B21" s="71"/>
-    </row>
-    <row r="22" spans="2:10">
-      <c r="B22" s="71"/>
-    </row>
-    <row r="23" spans="2:10">
-      <c r="B23" s="71"/>
-    </row>
-    <row r="24" spans="2:10" ht="17" thickBot="1">
-      <c r="B24" s="71"/>
-    </row>
-    <row r="25" spans="2:10" s="79" customFormat="1" ht="17" thickBot="1">
-      <c r="B25" s="71"/>
-      <c r="C25" s="80" t="s">
-        <v>51</v>
-      </c>
-      <c r="D25" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="E25" s="82">
-        <v>624.79999999999995</v>
-      </c>
-      <c r="F25" s="81" t="s">
-        <v>54</v>
-      </c>
-      <c r="G25" s="81"/>
-      <c r="H25" s="81"/>
-      <c r="I25" s="81"/>
-    </row>
-    <row r="26" spans="2:10" s="79" customFormat="1" ht="17" thickBot="1">
-      <c r="B26" s="71"/>
-      <c r="C26" s="81"/>
-      <c r="D26" s="81"/>
-      <c r="E26" s="81">
-        <f>E25*1000000</f>
-        <v>624800000</v>
-      </c>
-      <c r="F26" s="81" t="s">
-        <v>53</v>
-      </c>
-      <c r="G26" s="81"/>
-      <c r="H26" s="81"/>
-      <c r="I26" s="81"/>
-    </row>
-    <row r="27" spans="2:10" s="79" customFormat="1" ht="17" thickBot="1">
-      <c r="B27" s="71"/>
-      <c r="C27" s="81"/>
-      <c r="D27" s="81" t="s">
-        <v>60</v>
-      </c>
-      <c r="E27" s="83">
-        <f>5.8-0.9+3.96</f>
-        <v>8.86</v>
-      </c>
-      <c r="F27" s="81" t="s">
-        <v>63</v>
-      </c>
-      <c r="G27" s="81"/>
-      <c r="H27" s="81"/>
-      <c r="I27" s="81"/>
-    </row>
-    <row r="28" spans="2:10" s="79" customFormat="1">
-      <c r="B28" s="71"/>
-      <c r="C28" s="81"/>
-      <c r="D28" s="81"/>
-      <c r="E28" s="84">
-        <f>E27*1000000000</f>
-        <v>8860000000</v>
-      </c>
-      <c r="F28" s="81" t="s">
-        <v>60</v>
-      </c>
-      <c r="G28" s="81"/>
-      <c r="H28" s="81"/>
-      <c r="I28" s="81"/>
-    </row>
-    <row r="29" spans="2:10" s="79" customFormat="1">
-      <c r="B29" s="71"/>
-      <c r="C29" s="81"/>
-      <c r="D29" s="81"/>
-      <c r="E29" s="81"/>
-      <c r="F29" s="81"/>
-      <c r="G29" s="81"/>
-      <c r="H29" s="81"/>
-      <c r="I29" s="81" t="s">
-        <v>64</v>
-      </c>
-      <c r="J29" s="79" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30" spans="2:10" s="79" customFormat="1">
-      <c r="B30" s="71"/>
-      <c r="C30" s="81"/>
-      <c r="D30" s="81"/>
-      <c r="E30" s="85">
-        <f>E28/E26</f>
-        <v>14.180537772087067</v>
-      </c>
-      <c r="F30" s="81" t="s">
-        <v>61</v>
-      </c>
-      <c r="G30" s="81"/>
-      <c r="H30" s="81"/>
-      <c r="I30" s="81"/>
-      <c r="J30" s="79" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="31" spans="2:10" s="79" customFormat="1">
-      <c r="B31" s="71"/>
-      <c r="C31" s="81"/>
-      <c r="D31" s="81"/>
-      <c r="E31" s="81"/>
-      <c r="F31" s="81"/>
-      <c r="G31" s="81"/>
-      <c r="H31" s="81"/>
-      <c r="I31" s="81"/>
-      <c r="J31" s="79" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="32" spans="2:10" s="79" customFormat="1">
-      <c r="B32" s="71"/>
-      <c r="C32" s="81"/>
-      <c r="D32" s="81"/>
-      <c r="E32" s="81"/>
-      <c r="F32" s="81"/>
-      <c r="G32" s="81"/>
-      <c r="H32" s="81"/>
-      <c r="I32" s="81"/>
-      <c r="J32" s="79" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="33" spans="2:10" s="79" customFormat="1">
-      <c r="B33" s="71"/>
-      <c r="C33" s="81"/>
-      <c r="D33" s="81"/>
-      <c r="E33" s="81"/>
-      <c r="F33" s="81"/>
-      <c r="G33" s="81"/>
-      <c r="H33" s="81"/>
-      <c r="I33" s="81"/>
-      <c r="J33" s="79" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="34" spans="2:10" s="79" customFormat="1">
-      <c r="B34" s="71"/>
-      <c r="C34" s="81"/>
-      <c r="D34" s="81" t="str">
+      <c r="D17" s="80" t="str">
         <f>Dashboard!C11</f>
         <v>output.passenger_kms</v>
       </c>
-      <c r="E34" s="81">
-        <f>E30*E12</f>
-        <v>2.8361075544174135</v>
-      </c>
-      <c r="F34" s="81" t="s">
-        <v>62</v>
-      </c>
-      <c r="G34" s="81"/>
-      <c r="H34" s="57" t="s">
-        <v>40</v>
-      </c>
-      <c r="I34" s="81"/>
-    </row>
-    <row r="35" spans="2:10" s="79" customFormat="1">
+      <c r="E17" s="68">
+        <f>ROUND(E14*E12, 6)</f>
+        <v>1.7630429999999999</v>
+      </c>
+      <c r="F17" s="80" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9">
+      <c r="B18" s="71"/>
+    </row>
+    <row r="19" spans="2:9">
+      <c r="B19" s="71"/>
+    </row>
+    <row r="20" spans="2:9">
+      <c r="B20" s="71"/>
+    </row>
+    <row r="21" spans="2:9">
+      <c r="B21" s="71"/>
+    </row>
+    <row r="22" spans="2:9">
+      <c r="B22" s="71"/>
+    </row>
+    <row r="23" spans="2:9">
+      <c r="B23" s="71"/>
+    </row>
+    <row r="24" spans="2:9">
+      <c r="B24" s="71"/>
+      <c r="C24" s="79"/>
+      <c r="D24" s="79"/>
+      <c r="E24" s="79"/>
+      <c r="F24" s="79"/>
+      <c r="G24" s="79"/>
+    </row>
+    <row r="25" spans="2:9" s="79" customFormat="1">
+      <c r="B25" s="71"/>
+      <c r="H25" s="80"/>
+      <c r="I25" s="80"/>
+    </row>
+    <row r="26" spans="2:9" s="79" customFormat="1">
+      <c r="B26" s="71"/>
+      <c r="H26" s="80"/>
+      <c r="I26" s="80"/>
+    </row>
+    <row r="27" spans="2:9" s="79" customFormat="1">
+      <c r="B27" s="71"/>
+      <c r="H27" s="80"/>
+      <c r="I27" s="80"/>
+    </row>
+    <row r="28" spans="2:9" s="79" customFormat="1">
+      <c r="B28" s="71"/>
+      <c r="H28" s="80"/>
+      <c r="I28" s="80"/>
+    </row>
+    <row r="29" spans="2:9" s="79" customFormat="1">
+      <c r="B29" s="71"/>
+      <c r="H29" s="80"/>
+      <c r="I29" s="80"/>
+    </row>
+    <row r="30" spans="2:9" s="79" customFormat="1">
+      <c r="B30" s="71"/>
+      <c r="H30" s="80"/>
+      <c r="I30" s="80"/>
+    </row>
+    <row r="31" spans="2:9" s="79" customFormat="1">
+      <c r="B31" s="71"/>
+      <c r="H31" s="80"/>
+      <c r="I31" s="80"/>
+    </row>
+    <row r="32" spans="2:9" s="79" customFormat="1">
+      <c r="B32" s="71"/>
+      <c r="C32" s="80"/>
+      <c r="D32" s="80"/>
+      <c r="E32" s="80"/>
+      <c r="F32" s="80"/>
+      <c r="G32" s="80"/>
+      <c r="H32" s="80"/>
+      <c r="I32" s="80"/>
+    </row>
+    <row r="33" spans="2:9" s="79" customFormat="1">
+      <c r="B33" s="71"/>
+      <c r="C33" s="80"/>
+      <c r="D33" s="80"/>
+      <c r="E33" s="80"/>
+      <c r="F33" s="80"/>
+      <c r="G33" s="80"/>
+      <c r="H33" s="80"/>
+      <c r="I33" s="80"/>
+    </row>
+    <row r="34" spans="2:9" s="79" customFormat="1">
+      <c r="B34" s="71"/>
+      <c r="C34" s="80"/>
+      <c r="I34" s="80"/>
+    </row>
+    <row r="35" spans="2:9" s="79" customFormat="1">
       <c r="B35" s="71"/>
-      <c r="C35" s="81"/>
-      <c r="D35" s="81"/>
-      <c r="E35" s="81"/>
-      <c r="F35" s="81"/>
-      <c r="G35" s="81"/>
-      <c r="I35" s="81"/>
-    </row>
-    <row r="36" spans="2:10" s="79" customFormat="1">
+      <c r="C35" s="80"/>
+      <c r="D35" s="80"/>
+      <c r="E35" s="80"/>
+      <c r="F35" s="80"/>
+      <c r="G35" s="80"/>
+      <c r="I35" s="80"/>
+    </row>
+    <row r="36" spans="2:9" s="79" customFormat="1">
       <c r="B36" s="71"/>
-      <c r="C36" s="81"/>
-      <c r="D36" s="81"/>
-      <c r="E36" s="81"/>
-      <c r="F36" s="81"/>
-      <c r="G36" s="81"/>
-      <c r="I36" s="81"/>
-    </row>
-    <row r="37" spans="2:10" s="79" customFormat="1">
+      <c r="C36" s="80"/>
+      <c r="D36" s="80"/>
+      <c r="E36" s="80"/>
+      <c r="F36" s="80"/>
+      <c r="G36" s="80"/>
+      <c r="I36" s="80"/>
+    </row>
+    <row r="37" spans="2:9" s="79" customFormat="1">
       <c r="B37" s="71"/>
-      <c r="C37" s="81"/>
-      <c r="D37" s="81"/>
-      <c r="E37" s="81"/>
-      <c r="F37" s="81"/>
-      <c r="G37" s="81"/>
-      <c r="I37" s="81"/>
-    </row>
-    <row r="38" spans="2:10" s="79" customFormat="1">
+      <c r="C37" s="80"/>
+      <c r="D37" s="80"/>
+      <c r="E37" s="80"/>
+      <c r="F37" s="80"/>
+      <c r="G37" s="80"/>
+      <c r="I37" s="80"/>
+    </row>
+    <row r="38" spans="2:9" s="79" customFormat="1">
       <c r="B38" s="71"/>
     </row>
-    <row r="39" spans="2:10" s="79" customFormat="1">
+    <row r="39" spans="2:9" s="79" customFormat="1">
       <c r="B39" s="71"/>
     </row>
-    <row r="40" spans="2:10" s="79" customFormat="1">
+    <row r="40" spans="2:9" s="79" customFormat="1">
       <c r="B40" s="71"/>
     </row>
-    <row r="41" spans="2:10" s="79" customFormat="1">
+    <row r="41" spans="2:9" s="79" customFormat="1">
       <c r="B41" s="71"/>
     </row>
-    <row r="42" spans="2:10" s="79" customFormat="1">
+    <row r="42" spans="2:9" s="79" customFormat="1">
       <c r="B42" s="71"/>
     </row>
-    <row r="43" spans="2:10" s="79" customFormat="1">
+    <row r="43" spans="2:9" s="79" customFormat="1">
       <c r="B43" s="71"/>
     </row>
-    <row r="44" spans="2:10" s="79" customFormat="1">
+    <row r="44" spans="2:9" s="79" customFormat="1">
       <c r="B44" s="71"/>
     </row>
-    <row r="45" spans="2:10" s="79" customFormat="1">
+    <row r="45" spans="2:9" s="79" customFormat="1">
       <c r="B45" s="71"/>
     </row>
-    <row r="46" spans="2:10" s="79" customFormat="1">
+    <row r="46" spans="2:9" s="79" customFormat="1">
       <c r="B46" s="71"/>
     </row>
-    <row r="47" spans="2:10" s="79" customFormat="1">
+    <row r="47" spans="2:9" s="79" customFormat="1">
       <c r="B47" s="71"/>
     </row>
-    <row r="48" spans="2:10" s="79" customFormat="1">
+    <row r="48" spans="2:9" s="79" customFormat="1">
       <c r="B48" s="71"/>
     </row>
     <row r="49" spans="2:2" s="79" customFormat="1">
@@ -4532,71 +4075,71 @@
     <row r="80" spans="2:2">
       <c r="B80" s="71"/>
     </row>
-    <row r="81" spans="2:4" s="93" customFormat="1">
-      <c r="B81" s="94"/>
-    </row>
-    <row r="82" spans="2:4" s="93" customFormat="1">
-      <c r="B82" s="94"/>
-    </row>
-    <row r="83" spans="2:4" s="93" customFormat="1">
-      <c r="B83" s="94"/>
+    <row r="81" spans="2:4" s="88" customFormat="1">
+      <c r="B81" s="89"/>
+    </row>
+    <row r="82" spans="2:4" s="88" customFormat="1">
+      <c r="B82" s="89"/>
+    </row>
+    <row r="83" spans="2:4" s="88" customFormat="1">
+      <c r="B83" s="89"/>
       <c r="C83" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="84" spans="2:4" s="93" customFormat="1">
-      <c r="B84" s="94"/>
-      <c r="C84" s="93" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="85" spans="2:4" s="93" customFormat="1">
-      <c r="B85" s="94"/>
-    </row>
-    <row r="86" spans="2:4" s="93" customFormat="1">
-      <c r="B86" s="94"/>
-    </row>
-    <row r="87" spans="2:4" s="93" customFormat="1">
-      <c r="B87" s="94"/>
-    </row>
-    <row r="88" spans="2:4" s="93" customFormat="1">
-      <c r="B88" s="94"/>
-    </row>
-    <row r="89" spans="2:4" s="93" customFormat="1">
-      <c r="B89" s="94"/>
-      <c r="C89" s="93">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4" s="88" customFormat="1">
+      <c r="B84" s="89"/>
+      <c r="C84" s="88" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4" s="88" customFormat="1">
+      <c r="B85" s="89"/>
+    </row>
+    <row r="86" spans="2:4" s="88" customFormat="1">
+      <c r="B86" s="89"/>
+    </row>
+    <row r="87" spans="2:4" s="88" customFormat="1">
+      <c r="B87" s="89"/>
+    </row>
+    <row r="88" spans="2:4" s="88" customFormat="1">
+      <c r="B88" s="89"/>
+    </row>
+    <row r="89" spans="2:4" s="88" customFormat="1">
+      <c r="B89" s="89"/>
+      <c r="C89" s="88">
         <v>14</v>
       </c>
-      <c r="D89" s="93" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="90" spans="2:4" s="93" customFormat="1">
-      <c r="B90" s="94"/>
-    </row>
-    <row r="91" spans="2:4" s="93" customFormat="1">
-      <c r="B91" s="94"/>
-    </row>
-    <row r="92" spans="2:4" s="93" customFormat="1">
-      <c r="B92" s="94"/>
-    </row>
-    <row r="93" spans="2:4" s="93" customFormat="1">
-      <c r="B93" s="94"/>
-    </row>
-    <row r="94" spans="2:4" s="93" customFormat="1">
-      <c r="B94" s="94"/>
-    </row>
-    <row r="95" spans="2:4" s="93" customFormat="1">
-      <c r="B95" s="94"/>
-    </row>
-    <row r="96" spans="2:4" s="93" customFormat="1">
-      <c r="B96" s="94"/>
-    </row>
-    <row r="97" spans="2:7" s="93" customFormat="1">
-      <c r="B97" s="94"/>
-    </row>
-    <row r="98" spans="2:7" s="93" customFormat="1">
-      <c r="B98" s="94"/>
+      <c r="D89" s="88" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4" s="88" customFormat="1">
+      <c r="B90" s="89"/>
+    </row>
+    <row r="91" spans="2:4" s="88" customFormat="1">
+      <c r="B91" s="89"/>
+    </row>
+    <row r="92" spans="2:4" s="88" customFormat="1">
+      <c r="B92" s="89"/>
+    </row>
+    <row r="93" spans="2:4" s="88" customFormat="1">
+      <c r="B93" s="89"/>
+    </row>
+    <row r="94" spans="2:4" s="88" customFormat="1">
+      <c r="B94" s="89"/>
+    </row>
+    <row r="95" spans="2:4" s="88" customFormat="1">
+      <c r="B95" s="89"/>
+    </row>
+    <row r="96" spans="2:4" s="88" customFormat="1">
+      <c r="B96" s="89"/>
+    </row>
+    <row r="97" spans="2:7" s="88" customFormat="1">
+      <c r="B97" s="89"/>
+    </row>
+    <row r="98" spans="2:7" s="88" customFormat="1">
+      <c r="B98" s="89"/>
     </row>
     <row r="99" spans="2:7">
       <c r="B99" s="71"/>
@@ -4605,306 +4148,306 @@
       <c r="B100" s="71"/>
     </row>
     <row r="101" spans="2:7">
-      <c r="B101" s="94"/>
+      <c r="B101" s="89"/>
     </row>
     <row r="102" spans="2:7">
-      <c r="B102" s="94"/>
+      <c r="B102" s="89"/>
     </row>
     <row r="103" spans="2:7">
-      <c r="B103" s="94"/>
+      <c r="B103" s="89"/>
       <c r="C103" s="9" t="s">
-        <v>114</v>
+        <v>89</v>
       </c>
     </row>
     <row r="104" spans="2:7">
-      <c r="B104" s="94"/>
-      <c r="C104" s="108" t="s">
-        <v>115</v>
+      <c r="B104" s="89"/>
+      <c r="C104" s="103" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="105" spans="2:7">
-      <c r="B105" s="94"/>
-      <c r="C105" s="108"/>
+      <c r="B105" s="89"/>
+      <c r="C105" s="103"/>
     </row>
     <row r="106" spans="2:7" ht="17" thickBot="1">
-      <c r="B106" s="94"/>
+      <c r="B106" s="89"/>
     </row>
     <row r="107" spans="2:7" ht="17" thickBot="1">
-      <c r="B107" s="94"/>
-      <c r="D107" s="109" t="s">
-        <v>78</v>
-      </c>
-      <c r="E107" s="110">
+      <c r="B107" s="89"/>
+      <c r="D107" s="104" t="s">
+        <v>53</v>
+      </c>
+      <c r="E107" s="105">
         <v>216</v>
       </c>
-      <c r="F107" s="111" t="s">
-        <v>116</v>
-      </c>
-      <c r="G107" s="111"/>
+      <c r="F107" s="106" t="s">
+        <v>91</v>
+      </c>
+      <c r="G107" s="106"/>
     </row>
     <row r="108" spans="2:7" ht="17" thickBot="1">
-      <c r="B108" s="94"/>
-      <c r="D108" s="109"/>
-      <c r="E108" s="110">
+      <c r="B108" s="89"/>
+      <c r="D108" s="104"/>
+      <c r="E108" s="105">
         <f>E107/1000</f>
         <v>0.216</v>
       </c>
-      <c r="F108" s="111" t="s">
-        <v>79</v>
-      </c>
-      <c r="G108" s="111"/>
+      <c r="F108" s="106" t="s">
+        <v>54</v>
+      </c>
+      <c r="G108" s="106"/>
     </row>
     <row r="109" spans="2:7" ht="17" thickBot="1">
-      <c r="B109" s="94"/>
-      <c r="D109" s="109" t="s">
-        <v>84</v>
-      </c>
-      <c r="E109" s="110">
+      <c r="B109" s="89"/>
+      <c r="D109" s="104" t="s">
+        <v>59</v>
+      </c>
+      <c r="E109" s="105">
         <v>320</v>
       </c>
-      <c r="F109" s="111" t="s">
-        <v>117</v>
-      </c>
-      <c r="G109" s="111"/>
+      <c r="F109" s="106" t="s">
+        <v>92</v>
+      </c>
+      <c r="G109" s="106"/>
     </row>
     <row r="110" spans="2:7" ht="17" thickBot="1">
-      <c r="B110" s="94"/>
-      <c r="E110" s="110">
+      <c r="B110" s="89"/>
+      <c r="E110" s="105">
         <f>E109/1000</f>
         <v>0.32</v>
       </c>
-      <c r="F110" s="111" t="s">
-        <v>85</v>
-      </c>
-      <c r="G110" s="111"/>
+      <c r="F110" s="106" t="s">
+        <v>60</v>
+      </c>
+      <c r="G110" s="106"/>
     </row>
     <row r="111" spans="2:7" ht="17" thickBot="1">
-      <c r="B111" s="94"/>
-      <c r="D111" s="111" t="s">
-        <v>113</v>
-      </c>
-      <c r="E111" s="112">
+      <c r="B111" s="89"/>
+      <c r="D111" s="106" t="s">
+        <v>88</v>
+      </c>
+      <c r="E111" s="107">
         <f>E110</f>
         <v>0.32</v>
       </c>
-      <c r="F111" s="111" t="s">
-        <v>85</v>
-      </c>
-      <c r="G111" s="111" t="s">
-        <v>118</v>
+      <c r="F111" s="106" t="s">
+        <v>60</v>
+      </c>
+      <c r="G111" s="106" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="112" spans="2:7">
-      <c r="B112" s="94"/>
+      <c r="B112" s="89"/>
     </row>
     <row r="113" spans="2:3">
-      <c r="B113" s="94"/>
+      <c r="B113" s="89"/>
     </row>
     <row r="114" spans="2:3">
-      <c r="B114" s="94"/>
+      <c r="B114" s="89"/>
     </row>
     <row r="115" spans="2:3">
-      <c r="B115" s="94"/>
+      <c r="B115" s="89"/>
     </row>
     <row r="116" spans="2:3">
-      <c r="B116" s="94"/>
+      <c r="B116" s="89"/>
     </row>
     <row r="117" spans="2:3">
-      <c r="B117" s="94"/>
+      <c r="B117" s="89"/>
     </row>
     <row r="118" spans="2:3">
-      <c r="B118" s="94"/>
+      <c r="B118" s="89"/>
     </row>
     <row r="119" spans="2:3">
-      <c r="B119" s="94"/>
+      <c r="B119" s="89"/>
     </row>
     <row r="120" spans="2:3">
-      <c r="B120" s="94"/>
+      <c r="B120" s="89"/>
     </row>
     <row r="121" spans="2:3">
-      <c r="B121" s="94"/>
+      <c r="B121" s="89"/>
     </row>
     <row r="122" spans="2:3">
-      <c r="B122" s="94"/>
+      <c r="B122" s="89"/>
     </row>
     <row r="123" spans="2:3">
-      <c r="B123" s="94"/>
+      <c r="B123" s="89"/>
     </row>
     <row r="124" spans="2:3">
-      <c r="B124" s="94"/>
+      <c r="B124" s="89"/>
     </row>
     <row r="125" spans="2:3">
-      <c r="B125" s="94"/>
+      <c r="B125" s="89"/>
     </row>
     <row r="126" spans="2:3">
-      <c r="B126" s="94"/>
+      <c r="B126" s="89"/>
     </row>
     <row r="127" spans="2:3">
-      <c r="B127" s="94"/>
+      <c r="B127" s="89"/>
       <c r="C127" s="9" t="s">
-        <v>119</v>
+        <v>94</v>
       </c>
     </row>
     <row r="128" spans="2:3">
-      <c r="B128" s="94"/>
+      <c r="B128" s="89"/>
       <c r="C128" s="68" t="s">
-        <v>120</v>
+        <v>95</v>
       </c>
     </row>
     <row r="129" spans="2:5">
-      <c r="B129" s="94"/>
+      <c r="B129" s="89"/>
       <c r="C129" s="68" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
     </row>
     <row r="130" spans="2:5" ht="17" thickBot="1">
-      <c r="B130" s="94"/>
+      <c r="B130" s="89"/>
     </row>
     <row r="131" spans="2:5" ht="17" thickBot="1">
-      <c r="B131" s="94"/>
-      <c r="D131" s="153" t="s">
-        <v>140</v>
-      </c>
-      <c r="E131" s="113">
+      <c r="B131" s="89"/>
+      <c r="D131" s="134" t="s">
+        <v>114</v>
+      </c>
+      <c r="E131" s="108">
         <v>0.04</v>
       </c>
     </row>
     <row r="132" spans="2:5" ht="17" thickBot="1">
-      <c r="B132" s="94"/>
+      <c r="B132" s="89"/>
       <c r="D132" s="68" t="s">
-        <v>122</v>
-      </c>
-      <c r="E132" s="114">
+        <v>97</v>
+      </c>
+      <c r="E132" s="109">
         <f>1-(1-E131)^(1/(24*31))</f>
         <v>5.4866766968530989E-5</v>
       </c>
     </row>
     <row r="133" spans="2:5">
-      <c r="B133" s="94"/>
+      <c r="B133" s="89"/>
     </row>
     <row r="134" spans="2:5">
-      <c r="B134" s="94"/>
+      <c r="B134" s="89"/>
     </row>
     <row r="135" spans="2:5">
-      <c r="B135" s="94"/>
-      <c r="E135" s="154"/>
+      <c r="B135" s="89"/>
+      <c r="E135" s="135"/>
     </row>
     <row r="136" spans="2:5">
-      <c r="B136" s="94"/>
+      <c r="B136" s="89"/>
     </row>
     <row r="137" spans="2:5">
-      <c r="B137" s="94"/>
+      <c r="B137" s="89"/>
     </row>
     <row r="138" spans="2:5">
-      <c r="B138" s="94"/>
+      <c r="B138" s="89"/>
     </row>
     <row r="139" spans="2:5">
-      <c r="B139" s="94"/>
+      <c r="B139" s="89"/>
     </row>
     <row r="140" spans="2:5">
-      <c r="B140" s="94"/>
+      <c r="B140" s="89"/>
     </row>
     <row r="141" spans="2:5">
-      <c r="B141" s="94"/>
+      <c r="B141" s="89"/>
     </row>
     <row r="142" spans="2:5">
-      <c r="B142" s="94"/>
+      <c r="B142" s="89"/>
     </row>
     <row r="143" spans="2:5">
-      <c r="B143" s="94"/>
+      <c r="B143" s="89"/>
     </row>
     <row r="144" spans="2:5">
-      <c r="B144" s="94"/>
+      <c r="B144" s="89"/>
     </row>
     <row r="145" spans="2:2">
-      <c r="B145" s="94"/>
+      <c r="B145" s="89"/>
     </row>
     <row r="146" spans="2:2">
-      <c r="B146" s="94"/>
+      <c r="B146" s="89"/>
     </row>
     <row r="147" spans="2:2">
-      <c r="B147" s="94"/>
+      <c r="B147" s="89"/>
     </row>
     <row r="148" spans="2:2">
-      <c r="B148" s="94"/>
+      <c r="B148" s="89"/>
     </row>
     <row r="149" spans="2:2">
-      <c r="B149" s="94"/>
+      <c r="B149" s="89"/>
     </row>
     <row r="150" spans="2:2">
-      <c r="B150" s="94"/>
+      <c r="B150" s="89"/>
     </row>
     <row r="151" spans="2:2">
-      <c r="B151" s="94"/>
+      <c r="B151" s="89"/>
     </row>
     <row r="152" spans="2:2">
-      <c r="B152" s="94"/>
+      <c r="B152" s="89"/>
     </row>
     <row r="153" spans="2:2">
-      <c r="B153" s="94"/>
+      <c r="B153" s="89"/>
     </row>
     <row r="154" spans="2:2">
-      <c r="B154" s="94"/>
+      <c r="B154" s="89"/>
     </row>
     <row r="155" spans="2:2">
-      <c r="B155" s="94"/>
+      <c r="B155" s="89"/>
     </row>
     <row r="156" spans="2:2">
-      <c r="B156" s="94"/>
+      <c r="B156" s="89"/>
     </row>
     <row r="157" spans="2:2">
-      <c r="B157" s="94"/>
+      <c r="B157" s="89"/>
     </row>
     <row r="158" spans="2:2">
-      <c r="B158" s="94"/>
+      <c r="B158" s="89"/>
     </row>
     <row r="159" spans="2:2">
-      <c r="B159" s="94"/>
+      <c r="B159" s="89"/>
     </row>
     <row r="160" spans="2:2">
-      <c r="B160" s="94"/>
+      <c r="B160" s="89"/>
     </row>
     <row r="161" spans="2:2">
-      <c r="B161" s="94"/>
+      <c r="B161" s="89"/>
     </row>
     <row r="162" spans="2:2">
-      <c r="B162" s="94"/>
+      <c r="B162" s="89"/>
     </row>
     <row r="163" spans="2:2">
-      <c r="B163" s="94"/>
+      <c r="B163" s="89"/>
     </row>
     <row r="164" spans="2:2">
-      <c r="B164" s="94"/>
+      <c r="B164" s="89"/>
     </row>
     <row r="165" spans="2:2">
-      <c r="B165" s="94"/>
+      <c r="B165" s="89"/>
     </row>
     <row r="166" spans="2:2">
-      <c r="B166" s="94"/>
+      <c r="B166" s="89"/>
     </row>
     <row r="167" spans="2:2">
-      <c r="B167" s="94"/>
+      <c r="B167" s="89"/>
     </row>
     <row r="168" spans="2:2">
-      <c r="B168" s="94"/>
+      <c r="B168" s="89"/>
     </row>
     <row r="169" spans="2:2">
-      <c r="B169" s="94"/>
+      <c r="B169" s="89"/>
     </row>
     <row r="170" spans="2:2">
-      <c r="B170" s="94"/>
+      <c r="B170" s="89"/>
     </row>
     <row r="171" spans="2:2">
-      <c r="B171" s="94"/>
+      <c r="B171" s="89"/>
     </row>
     <row r="172" spans="2:2">
-      <c r="B172" s="94"/>
+      <c r="B172" s="89"/>
     </row>
     <row r="173" spans="2:2">
-      <c r="B173" s="94"/>
+      <c r="B173" s="89"/>
     </row>
     <row r="174" spans="2:2">
-      <c r="B174" s="94"/>
+      <c r="B174" s="89"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
